--- a/data/trans_bre/P3A_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,37</t>
+          <t>-3,4; 0,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,45</t>
+          <t>-2,69; 0,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,84</t>
+          <t>-2,6; 0,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,66</t>
+          <t>-5,34; 1,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 29,23</t>
+          <t>-80,74; 41,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,48; 113,55</t>
+          <t>-81,78; 74,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,87; 130,82</t>
+          <t>-91,52; 122,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 200,15</t>
+          <t>-92,48; 244,58</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,22</t>
+          <t>-3,03; 0,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,3</t>
+          <t>-1,58; 1,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,14</t>
+          <t>-0,13; 2,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,09</t>
+          <t>-2,72; 1,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,32; 14,91</t>
+          <t>-74,26; 21,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,75; 105,15</t>
+          <t>-64,36; 134,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-92,59; —</t>
+          <t>-79,37; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -1,01</t>
+          <t>-5,3; -0,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,89</t>
+          <t>-1,82; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,39</t>
+          <t>-1,01; 1,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,48</t>
+          <t>-2,22; 0,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-76,32; -21,93</t>
+          <t>-76,14; -16,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,25; 132,04</t>
+          <t>-54,99; 109,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 295,99</t>
+          <t>-71,91; 278,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-78,69; 61,06</t>
+          <t>-79,46; 70,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -0,01</t>
+          <t>-4,41; 0,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,12</t>
+          <t>-2,09; 1,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,29</t>
+          <t>-1,09; 1,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,92</t>
+          <t>-0,87; 2,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,22; 9,64</t>
+          <t>-81,74; 13,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 109,44</t>
+          <t>-57,02; 114,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 257,55</t>
+          <t>-67,39; 228,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 285,99</t>
+          <t>-30,74; 242,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,76</t>
+          <t>-4,07; 0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,96</t>
+          <t>-1,23; 3,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,38</t>
+          <t>-5,02; -0,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,13</t>
+          <t>-2,57; 1,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-79,8; 47,3</t>
+          <t>-77,99; 65,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 199,29</t>
+          <t>-36,8; 226,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-87,97; -7,06</t>
+          <t>-90,21; -9,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,68; 51,42</t>
+          <t>-57,04; 56,46</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,93</t>
+          <t>-0,48; 5,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 2,01</t>
+          <t>-5,48; 2,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,92</t>
+          <t>0,21; 5,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 1,55</t>
+          <t>-6,32; 1,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 395,22</t>
+          <t>-12,72; 341,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,94; 62,55</t>
+          <t>-61,69; 61,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 756,33</t>
+          <t>-15,39; 800,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,44; 24,47</t>
+          <t>-76,81; 25,68</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 6,26</t>
+          <t>-4,11; 6,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 8,07</t>
+          <t>-4,83; 8,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 7,01</t>
+          <t>-4,75; 6,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,83</t>
+          <t>0,89; 11,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 99,57</t>
+          <t>-33,93; 94,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 58,21</t>
+          <t>-22,66; 57,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 68,37</t>
+          <t>-29,13; 61,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 57,05</t>
+          <t>3,64; 58,53</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,0</t>
+          <t>-1,84; 0,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,78</t>
+          <t>-0,28; 1,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,52</t>
+          <t>-0,18; 1,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,2</t>
+          <t>-0,11; 2,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 1,25</t>
+          <t>-40,49; 1,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 53,72</t>
+          <t>-7,01; 54,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 73,74</t>
+          <t>-10,32; 65,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 60,26</t>
+          <t>-2,14; 61,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-36,52%</t>
+          <t>-46,3%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,38</t>
+          <t>-3,39; 0,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,99</t>
+          <t>-2,64; 1,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,82</t>
+          <t>-2,42; 0,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 1,77</t>
+          <t>-5,18; 1,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-80,74; 41,54</t>
+          <t>-79,56; 34,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,78; 74,06</t>
+          <t>-78,59; 110,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-91,52; 122,0</t>
+          <t>-88,9; 154,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-92,48; 244,58</t>
+          <t>-100,0; 186,8</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-6,16%</t>
+          <t>-2,01%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,3</t>
+          <t>-3,06; 0,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,41</t>
+          <t>-1,61; 1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,2</t>
+          <t>-0,22; 2,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,16</t>
+          <t>-3,06; 1,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,26; 21,13</t>
+          <t>-72,8; 13,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,36; 134,04</t>
+          <t>-64,16; 136,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,37; —</t>
+          <t>-68,67; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-41,24%</t>
+          <t>-32,06%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -0,83</t>
+          <t>-5,18; -0,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,72</t>
+          <t>-1,81; 1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,27</t>
+          <t>-0,86; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,5</t>
+          <t>-2,13; 0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-76,14; -16,76</t>
+          <t>-74,45; -18,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,99; 109,69</t>
+          <t>-54,6; 117,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 278,64</t>
+          <t>-66,74; 318,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,46; 70,09</t>
+          <t>-77,17; 71,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>-3,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,07</t>
+          <t>-4,14; 0,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,95</t>
+          <t>-2,12; 2,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,31</t>
+          <t>-1,11; 1,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,66</t>
+          <t>-2,0; 1,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,74; 13,6</t>
+          <t>-77,85; 21,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,02; 114,47</t>
+          <t>-57,89; 117,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 228,31</t>
+          <t>-67,23; 312,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 242,11</t>
+          <t>-47,89; 77,92</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-21,34%</t>
+          <t>-21,32%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,87</t>
+          <t>-4,08; 0,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,91</t>
+          <t>-1,32; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -0,37</t>
+          <t>-5,04; -0,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,24</t>
+          <t>-2,62; 0,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-77,99; 65,36</t>
+          <t>-80,84; 54,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 226,67</t>
+          <t>-36,4; 197,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-90,21; -9,19</t>
+          <t>-88,81; -5,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,04; 56,46</t>
+          <t>-57,53; 41,28</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-27,93%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,5</t>
+          <t>-0,62; 5,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 2,15</t>
+          <t>-5,68; 1,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,27</t>
+          <t>0,06; 4,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,54</t>
+          <t>-1,69; 3,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 341,47</t>
+          <t>-17,96; 324,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,69; 61,62</t>
+          <t>-66,05; 48,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 800,31</t>
+          <t>-10,37; 933,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,81; 25,68</t>
+          <t>-21,03; 78,07</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>6,44</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 6,33</t>
+          <t>-3,87; 6,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 8,2</t>
+          <t>-4,85; 8,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 6,81</t>
+          <t>-5,27; 6,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 11,19</t>
+          <t>1,07; 11,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 94,48</t>
+          <t>-31,99; 102,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 57,77</t>
+          <t>-23,06; 61,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 61,71</t>
+          <t>-30,88; 57,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 58,53</t>
+          <t>4,44; 61,65</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,05</t>
+          <t>-1,9; -0,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,78</t>
+          <t>-0,23; 1,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,43</t>
+          <t>-0,19; 1,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,23</t>
+          <t>0,19; 2,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 1,59</t>
+          <t>-40,95; -0,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 54,19</t>
+          <t>-5,08; 53,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 65,35</t>
+          <t>-7,53; 67,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 61,58</t>
+          <t>3,87; 54,63</t>
         </is>
       </c>
     </row>
